--- a/i_test/test_D6_Tabella_1_fasciaeta_2025/g_output/D6_Table_1_65-84.xlsx
+++ b/i_test/test_D6_Tabella_1_fasciaeta_2025/g_output/D6_Table_1_65-84.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,6 +375,11 @@
           <t>SE</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Tutte</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -397,6 +402,11 @@
           <t>SE</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Tutte</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -406,17 +416,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>507</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>591</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1665</t>
         </is>
       </c>
     </row>
@@ -428,17 +443,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>265 (47,6%)</t>
+          <t>248 (48,9%)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>291 (51,2%)</t>
+          <t>312 (52,8%)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>269 (49,8%)</t>
+          <t>265 (46,7%)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>825 (49,5%)</t>
         </is>
       </c>
     </row>
@@ -450,17 +470,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>44 (7,9%)</t>
+          <t>39 (7,7%)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>48 (8,5%)</t>
+          <t>48 (8,1%)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44 (8,1%)</t>
+          <t>42 (7,4%)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>129 (7,7%)</t>
         </is>
       </c>
     </row>
@@ -474,110 +499,135 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A10BD20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>163 (29,3%)</t>
+          <t>A10BD08 187 (0,4%)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>192 (33,8%)</t>
+          <t>A10BK 229 (0,4%)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>172 (31,9%)</t>
+          <t>A10BH 234 (0,4%)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>A10BH 597 (0,4%)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A10BD24</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>171 (30,7%)</t>
+          <t>A10BX16 187 (0,4%)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>176 (31,0%)</t>
+          <t>A10BD11 224 (0,4%)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>177 (32,8%)</t>
+          <t>A10BD20 219 (0,4%)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>A10BD19 592 (0,4%)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A10BK</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>188 (33,8%)</t>
+          <t>A10BD07 183 (0,4%)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>167 (29,4%)</t>
+          <t>A10BD21 218 (0,4%)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>158 (29,3%)</t>
+          <t>A10BD13 213 (0,4%)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>A10BK 588 (0,4%)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A10BD10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>160 (28,7%)</t>
+          <t>A10BK 181 (0,4%)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>189 (33,3%)</t>
+          <t>A10BD15 217 (0,4%)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>163 (30,2%)</t>
+          <t>A10BD23 206 (0,4%)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>A10BD20 586 (0,4%)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A10BD07</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>169 (30,3%)</t>
+          <t>A10BD16 180 (0,4%)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>176 (31,0%)</t>
+          <t>A10BD19 214 (0,4%)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>166 (30,7%)</t>
+          <t>A10BD16 202 (0,4%)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>A10BD11 582 (0,3%)</t>
         </is>
       </c>
     </row>
@@ -596,17 +646,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>280 (50,3%)</t>
+          <t>5 (1,0%)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>250 (44,0%)</t>
+          <t>6 (1,0%)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>248 (45,9%)</t>
+          <t>8 (1,4%)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>19 (1,1%)</t>
         </is>
       </c>
     </row>
@@ -625,17 +680,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>382 (68,6%)</t>
+          <t>328 (64,7%)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>393 (69,2%)</t>
+          <t>371 (62,8%)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>384 (71,1%)</t>
+          <t>351 (61,9%)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.050 (63,1%)</t>
         </is>
       </c>
     </row>
@@ -647,17 +707,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>376 (67,5%)</t>
+          <t>34 (6,7%)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>401 (70,6%)</t>
+          <t>48 (8,1%)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>354 (65,6%)</t>
+          <t>56 (9,9%)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>138 (8,3%)</t>
         </is>
       </c>
     </row>
@@ -669,17 +734,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>145 (26,0%)</t>
+          <t>325 (64,1%)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>140 (24,6%)</t>
+          <t>390 (66,0%)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>121 (22,4%)</t>
+          <t>338 (59,6%)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.053 (63,2%)</t>
         </is>
       </c>
     </row>
@@ -691,17 +761,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>331 (59,4%)</t>
+          <t>207 (40,8%)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>310 (54,6%)</t>
+          <t>281 (47,5%)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>329 (60,9%)</t>
+          <t>249 (43,9%)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>737 (44,3%)</t>
         </is>
       </c>
     </row>

--- a/i_test/test_D6_Tabella_1_fasciaeta_2025/g_output/D6_Table_1_65-84.xlsx
+++ b/i_test/test_D6_Tabella_1_fasciaeta_2025/g_output/D6_Table_1_65-84.xlsx
@@ -504,22 +504,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A10BD08 187 (0,4%)</t>
+          <t>ll 187 (36,9%)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A10BK 229 (0,4%)</t>
+          <t>NA 229 (38,7%)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A10BH 234 (0,4%)</t>
+          <t>NA 234 (41,3%)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>A10BH 597 (0,4%)</t>
+          <t>NA 597 (35,9%)</t>
         </is>
       </c>
     </row>
@@ -531,22 +531,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A10BX16 187 (0,4%)</t>
+          <t>cc 187 (36,9%)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A10BD11 224 (0,4%)</t>
+          <t>ii 224 (37,9%)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>A10BD20 219 (0,4%)</t>
+          <t>rr 219 (38,6%)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>A10BD19 592 (0,4%)</t>
+          <t>gg 592 (35,6%)</t>
         </is>
       </c>
     </row>
@@ -558,22 +558,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A10BD07 183 (0,4%)</t>
+          <t>kk 183 (36,1%)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A10BD21 218 (0,4%)</t>
+          <t>ff 218 (36,9%)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>A10BD13 213 (0,4%)</t>
+          <t>hh 213 (37,6%)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>A10BK 588 (0,4%)</t>
+          <t>NA 588 (35,3%)</t>
         </is>
       </c>
     </row>
@@ -585,22 +585,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A10BK 181 (0,4%)</t>
+          <t>NA 181 (35,7%)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A10BD15 217 (0,4%)</t>
+          <t>qq 217 (36,7%)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>A10BD23 206 (0,4%)</t>
+          <t>ss 206 (36,3%)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>A10BD20 586 (0,4%)</t>
+          <t>rr 586 (35,2%)</t>
         </is>
       </c>
     </row>
@@ -612,22 +612,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A10BD16 180 (0,4%)</t>
+          <t>pp 180 (35,5%)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A10BD19 214 (0,4%)</t>
+          <t>gg 214 (36,2%)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A10BD16 202 (0,4%)</t>
+          <t>pp 202 (35,6%)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>A10BD11 582 (0,3%)</t>
+          <t>ii 582 (35,0%)</t>
         </is>
       </c>
     </row>
